--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV18_aggregate_summary_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV18_aggregate_summary_data.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.112028167092407</v>
+        <v>4.252312658810234</v>
       </c>
       <c r="C3" t="n">
-        <v>4.100489477842044</v>
+        <v>4.243643963773404</v>
       </c>
     </row>
     <row r="4">
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4785079365778709</v>
+        <v>0.5222568310773773</v>
       </c>
       <c r="C4" t="n">
-        <v>0.489921092200338</v>
+        <v>0.5339338603030436</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.918220098454422</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.895402084252306</v>
+        <v>4.035612671936306</v>
       </c>
       <c r="C6" t="n">
-        <v>3.878033393753802</v>
+        <v>4.023161576669752</v>
       </c>
     </row>
     <row r="7">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.237294272053565</v>
+        <v>4.399756608100048</v>
       </c>
       <c r="C7" t="n">
-        <v>4.229881023321511</v>
+        <v>4.397793232880874</v>
       </c>
     </row>
     <row r="8">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.426583778948707</v>
+        <v>4.546166074231425</v>
       </c>
       <c r="C8" t="n">
-        <v>4.424874178675337</v>
+        <v>4.545073336433905</v>
       </c>
     </row>
     <row r="9">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.897014864588035</v>
+        <v>4.937016391583102</v>
       </c>
       <c r="C9" t="n">
-        <v>4.897014864588035</v>
+        <v>4.937016391583102</v>
       </c>
     </row>
   </sheetData>
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1644556160685193</v>
+        <v>0.3248266070846716</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1628846064329935</v>
+        <v>0.3223013545594191</v>
       </c>
     </row>
     <row r="3">
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7293324954615277</v>
+        <v>0.5788297723781595</v>
       </c>
       <c r="C3" t="n">
-        <v>0.726376669925057</v>
+        <v>0.5796792812921845</v>
       </c>
     </row>
     <row r="4">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1023018200437555</v>
+        <v>0.09181678536517246</v>
       </c>
       <c r="C4" t="n">
-        <v>0.10806218870735</v>
+        <v>0.09693711306614533</v>
       </c>
     </row>
     <row r="5">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003910068426197458</v>
+        <v>0.004526835171996462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002676534934599451</v>
+        <v>0.001082251082251082</v>
       </c>
     </row>
     <row r="6">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.657278145152389</v>
+        <v>4.747592481612863</v>
       </c>
       <c r="C2" t="n">
-        <v>4.657278145152389</v>
+        <v>4.747592481612863</v>
       </c>
     </row>
     <row r="3">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.305012807161345</v>
+        <v>4.434486848618672</v>
       </c>
       <c r="C3" t="n">
-        <v>4.214974323542153</v>
+        <v>4.369501739888368</v>
       </c>
     </row>
     <row r="4">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.122717745569459</v>
+        <v>4.170173267592935</v>
       </c>
       <c r="C4" t="n">
-        <v>4.073239732348722</v>
+        <v>4.155309745472008</v>
       </c>
     </row>
     <row r="5">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.020297711083841</v>
+        <v>4.754497918712521</v>
       </c>
       <c r="C5" t="n">
-        <v>4.020297711083841</v>
+        <v>4.754497918712521</v>
       </c>
     </row>
     <row r="6">
@@ -762,10 +762,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.688958301100911</v>
+        <v>4.562266853075351</v>
       </c>
       <c r="C6" t="n">
-        <v>4.688958301100911</v>
+        <v>4.562266853075351</v>
       </c>
     </row>
     <row r="7">
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.570699383583211</v>
+        <v>4.264827894530907</v>
       </c>
       <c r="C7" t="n">
-        <v>4.570699383583211</v>
+        <v>4.264827894530907</v>
       </c>
     </row>
     <row r="8">
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.906320565237385</v>
+        <v>3.565201986524612</v>
       </c>
       <c r="C8" t="n">
-        <v>3.78784280324228</v>
+        <v>3.512584820170524</v>
       </c>
     </row>
     <row r="9">
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.310991186301532</v>
+        <v>4.485365246893079</v>
       </c>
       <c r="C9" t="n">
-        <v>4.248062736565472</v>
+        <v>4.462795334676796</v>
       </c>
     </row>
     <row r="10">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.395531990916941</v>
+        <v>3.837483603060402</v>
       </c>
       <c r="C10" t="n">
-        <v>4.395531990916941</v>
+        <v>3.837483603060402</v>
       </c>
     </row>
     <row r="11">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.204411429911808</v>
+        <v>3.731831441947485</v>
       </c>
       <c r="C11" t="n">
-        <v>4.362769086133749</v>
+        <v>4.132911011564326</v>
       </c>
     </row>
     <row r="12">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.439602080737167</v>
+        <v>4.629090008283906</v>
       </c>
       <c r="C12" t="n">
-        <v>4.280445176366069</v>
+        <v>4.575088295257314</v>
       </c>
     </row>
     <row r="13">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.308899421545303</v>
+        <v>4.171813947427673</v>
       </c>
       <c r="C13" t="n">
-        <v>4.308899421545303</v>
+        <v>4.171813947427673</v>
       </c>
     </row>
     <row r="14">
@@ -866,10 +866,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.495185119311957</v>
+        <v>4.120176073927588</v>
       </c>
       <c r="C14" t="n">
-        <v>4.4593716864564</v>
+        <v>4.117054902857791</v>
       </c>
     </row>
     <row r="15">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.629885352729512</v>
+        <v>4.716012462047898</v>
       </c>
       <c r="C15" t="n">
-        <v>4.629885352729512</v>
+        <v>4.716012462047898</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV18_aggregate_summary_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV18_aggregate_summary_data.xlsx
@@ -447,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.252312658810234</v>
+        <v>4.249591863397385</v>
       </c>
       <c r="C3" t="n">
-        <v>4.243643963773404</v>
+        <v>4.241131070714376</v>
       </c>
     </row>
     <row r="4">
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5222568310773773</v>
+        <v>0.5270350006842635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5339338603030436</v>
+        <v>0.5382841145094548</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.035612671936306</v>
+        <v>4.033965651312452</v>
       </c>
       <c r="C6" t="n">
-        <v>4.023161576669752</v>
+        <v>4.020490590540712</v>
       </c>
     </row>
     <row r="7">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.399756608100048</v>
+        <v>4.400549799035751</v>
       </c>
       <c r="C7" t="n">
-        <v>4.397793232880874</v>
+        <v>4.398509318212247</v>
       </c>
     </row>
     <row r="8">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.546166074231425</v>
+        <v>4.546672341561328</v>
       </c>
       <c r="C8" t="n">
-        <v>4.545073336433905</v>
+        <v>4.545490576833773</v>
       </c>
     </row>
     <row r="9">
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3248266070846716</v>
+        <v>0.325687753107108</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3223013545594191</v>
+        <v>0.3231392263650328</v>
       </c>
     </row>
     <row r="3">
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5788297723781595</v>
+        <v>0.573686170460364</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5796792812921845</v>
+        <v>0.5746171391332682</v>
       </c>
     </row>
     <row r="4">
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09181678536517246</v>
+        <v>0.09605269282688637</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09693711306614533</v>
+        <v>0.1011148349858027</v>
       </c>
     </row>
     <row r="5">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004526835171996462</v>
+        <v>0.00457338360564167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001082251082251082</v>
+        <v>0.00112879951589629</v>
       </c>
     </row>
     <row r="6">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.747592481612863</v>
+        <v>4.751024533621168</v>
       </c>
       <c r="C2" t="n">
-        <v>4.747592481612863</v>
+        <v>4.751024533621168</v>
       </c>
     </row>
     <row r="3">
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.485365246893079</v>
+        <v>4.180074437129201</v>
       </c>
       <c r="C9" t="n">
-        <v>4.462795334676796</v>
+        <v>4.174292549579402</v>
       </c>
     </row>
     <row r="10">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.731831441947485</v>
+        <v>3.729678094352641</v>
       </c>
       <c r="C11" t="n">
-        <v>4.132911011564326</v>
+        <v>4.123510701297443</v>
       </c>
     </row>
     <row r="12">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.171813947427673</v>
+        <v>4.254047143739849</v>
       </c>
       <c r="C13" t="n">
-        <v>4.171813947427673</v>
+        <v>4.254047143739849</v>
       </c>
     </row>
     <row r="14">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
